--- a/public/Data_Guru_SMP_AlAzhar.xlsx
+++ b/public/Data_Guru_SMP_AlAzhar.xlsx
@@ -417,7 +417,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>NIP</v>
+        <v>NIY</v>
       </c>
       <c r="B1" t="str">
         <v>Nama Lengkap</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>NIP</v>
+        <v>NIY</v>
       </c>
       <c r="B2" t="str">
-        <v>Nomor Induk Pegawai</v>
+        <v>Nomor Induk Yayasan</v>
       </c>
       <c r="C2" t="str">
         <v>Opsional</v>
